--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136759775</v>
+        <v>136986410</v>
       </c>
       <c r="B2" t="n">
-        <v>98215</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +713,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skultuna, Vstm</t>
+          <t>Porsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574990</v>
+        <v>574897</v>
       </c>
       <c r="R2" t="n">
-        <v>6619104</v>
+        <v>6619041</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,16 +787,137 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136986410</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136759775</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skultuna, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>574990</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6619104</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136759775</t>
         </is>
@@ -802,6 +926,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986410</v>
       </c>
       <c r="B2" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986410</v>
       </c>
       <c r="B2" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986410</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136759775</v>
       </c>
       <c r="B3" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986410</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986410</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39918-2026 artfynd.xlsx
+++ b/artfynd/A 39918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986410</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
